--- a/output/汇总_实习练习-销售脏数据.xlsx
+++ b/output/汇总_实习练习-销售脏数据.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,10 +463,15 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>销售额校验</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>销售员</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>地区</t>
         </is>
@@ -507,10 +512,15 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>原数据正常</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>华东</t>
         </is>
@@ -551,10 +561,15 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>王芳</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>西南</t>
         </is>
@@ -591,10 +606,15 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>原数据正常</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>华东</t>
         </is>
@@ -635,10 +655,15 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>赵磊</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -675,10 +700,15 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -719,10 +749,15 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>赵磊</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>华东</t>
         </is>
@@ -763,10 +798,15 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>王芳</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>西南</t>
         </is>
@@ -807,10 +847,15 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>李娜</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -851,10 +896,15 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -895,10 +945,15 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>赵磊</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -935,10 +990,15 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>王芳</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -979,10 +1039,15 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>原数据正常</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>王芳</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -1023,10 +1088,15 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>原数据正常</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>王芳</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -1067,10 +1137,15 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>李娜</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>华东</t>
         </is>
@@ -1111,10 +1186,15 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>华南</t>
         </is>
@@ -1153,8 +1233,13 @@
       <c r="H17" t="n">
         <v>178</v>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -1195,10 +1280,15 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>赵磊</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -1239,10 +1329,15 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>李娜</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>西南</t>
         </is>
@@ -1269,30 +1364,29 @@
           <t>电脑整机</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>异常</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>异常</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>异常</t>
-        </is>
+      <c r="E20" t="n">
+        <v>9999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>59984001</v>
       </c>
       <c r="H20" t="n">
         <v>29995</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>华南</t>
         </is>
@@ -1333,10 +1427,15 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -1377,10 +1476,15 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>华东</t>
         </is>
@@ -1421,10 +1525,15 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>华东</t>
         </is>
@@ -1463,10 +1572,15 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>赵磊</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>西南</t>
         </is>
@@ -1507,10 +1621,15 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -1551,10 +1670,15 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>华南</t>
         </is>
@@ -1595,10 +1719,15 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -1639,10 +1768,15 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>华东</t>
         </is>
@@ -1683,10 +1817,15 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>华南</t>
         </is>
@@ -1727,10 +1866,15 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>赵磊</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>西南</t>
         </is>
@@ -1771,10 +1915,15 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
           <t>赵磊</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -1815,10 +1964,15 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
           <t>王芳</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -1857,10 +2011,15 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
           <t>李娜</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -1901,10 +2060,15 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>西南</t>
         </is>
@@ -1945,10 +2109,15 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>华东</t>
         </is>
@@ -1989,10 +2158,15 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -2019,10 +2193,8 @@
           <t>外设</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>异常</t>
-        </is>
+      <c r="E37" t="n">
+        <v>1</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2039,10 +2211,15 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -2083,10 +2260,15 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -2123,10 +2305,15 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
+          <t>原数据正常</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -2167,10 +2354,15 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>华南</t>
         </is>
@@ -2211,10 +2403,15 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
+          <t>原数据正常</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>华南</t>
         </is>
@@ -2251,10 +2448,15 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>华东</t>
         </is>
@@ -2295,10 +2497,15 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>西南</t>
         </is>
@@ -2339,10 +2546,15 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
           <t>赵磊</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -2383,10 +2595,15 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -2427,10 +2644,15 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -2471,10 +2693,15 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
           <t>李娜</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -2515,10 +2742,15 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
           <t>李娜</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -2559,10 +2791,15 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
           <t>李娜</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>华南</t>
         </is>
@@ -2603,10 +2840,15 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -2647,10 +2889,15 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>华东</t>
         </is>
@@ -2682,10 +2929,8 @@
           <t>异常</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>异常</t>
-        </is>
+      <c r="F52" t="n">
+        <v>79</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2697,10 +2942,15 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -2741,10 +2991,15 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -2785,10 +3040,15 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>华南</t>
         </is>
@@ -2829,10 +3089,15 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>西南</t>
         </is>
@@ -2873,10 +3138,15 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>华南</t>
         </is>
@@ -2917,10 +3187,15 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
+          <t>原数据正常</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
           <t>李娜</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>华东</t>
         </is>
@@ -2961,10 +3236,15 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -3005,10 +3285,15 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -3049,10 +3334,15 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -3093,10 +3383,15 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>华东</t>
         </is>
@@ -3137,10 +3432,15 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -3181,10 +3481,15 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
           <t>王芳</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -3225,10 +3530,15 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
           <t>王芳</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -3269,10 +3579,15 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
           <t>赵磊</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>西南</t>
         </is>
@@ -3313,10 +3628,15 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -3357,10 +3677,15 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
+          <t>原数据异常</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>华南</t>
         </is>
@@ -3399,7 +3724,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>509915</v>
+        <v>60493916</v>
       </c>
     </row>
     <row r="3">
@@ -3419,7 +3744,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69137</v>
+        <v>72725</v>
       </c>
     </row>
     <row r="5">
@@ -3429,7 +3754,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28619</v>
+        <v>28777</v>
       </c>
     </row>
   </sheetData>
@@ -3461,51 +3786,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>307277</v>
+        <v>60055129</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>165855</v>
+        <v>307277</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>119481</v>
+        <v>166013</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>104437</v>
+        <v>119481</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>71128</v>
+        <v>108025</v>
       </c>
     </row>
   </sheetData>
@@ -3537,21 +3862,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>王芳</t>
+          <t>刘强</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>211093</v>
+        <v>60183437</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>刘强</t>
+          <t>王芳</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>199436</v>
+        <v>211093</v>
       </c>
     </row>
     <row r="4">
@@ -3561,7 +3886,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>111078</v>
+        <v>114666</v>
       </c>
     </row>
     <row r="5">
@@ -3581,7 +3906,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>95143</v>
+        <v>95301</v>
       </c>
     </row>
     <row r="7">
@@ -3627,7 +3952,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>486038</v>
+        <v>60470039</v>
       </c>
     </row>
     <row r="3">
